--- a/rtss-pre1917/charts/birth-death-counts/adjusted-stage1-intermediate/Ферганская обл.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/adjusted-stage1-intermediate/Ферганская обл.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t xml:space="preserve">Числа рождений и смертей для </t>
   </si>
@@ -1956,10 +1956,10 @@
         <v>1881.0</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>40253.0</v>
+        <v>42498.0</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>26080.0</v>
+        <v>29809.0</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1994,7 +1994,7 @@
         <v>1883.0</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>28575.0</v>
+        <v>28574.0</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>19599.0</v>
@@ -2013,7 +2013,7 @@
         <v>1884.0</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>30897.0</v>
+        <v>30896.0</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>20951.0</v>
@@ -2108,10 +2108,10 @@
         <v>1889.0</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>14233.0</v>
+        <v>45351.0</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>9781.0</v>
+        <v>31809.0</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
